--- a/exel/users.xlsx
+++ b/exel/users.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
   <si>
     <t>Имя</t>
   </si>
@@ -47,10 +47,10 @@
     <t>Иван</t>
   </si>
   <si>
-    <t>Долбанов</t>
-  </si>
-  <si>
-    <t>Киргизович</t>
+    <t>Иванов</t>
+  </si>
+  <si>
+    <t>Иванович</t>
   </si>
   <si>
     <t>10Т</t>
@@ -59,28 +59,184 @@
     <t>Student</t>
   </si>
   <si>
-    <t>Вован</t>
-  </si>
-  <si>
-    <t>Вованов</t>
-  </si>
-  <si>
-    <t>10К</t>
+    <t>Владимир</t>
+  </si>
+  <si>
+    <t>Владимиров</t>
+  </si>
+  <si>
+    <t>Владимирович</t>
+  </si>
+  <si>
+    <t>10T</t>
   </si>
   <si>
     <t>Максим</t>
   </si>
   <si>
-    <t>Строганов</t>
+    <t>Максимов</t>
+  </si>
+  <si>
+    <t>Максимович</t>
+  </si>
+  <si>
+    <t>11Т 11К 10Т 10К 7З 7И 7Т 8З 8И 8Т 9З 9И 9Т</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>Евгения</t>
+  </si>
+  <si>
+    <t>Евгеньева</t>
+  </si>
+  <si>
+    <t>Евгеньевна</t>
+  </si>
+  <si>
+    <t>Екатерина</t>
+  </si>
+  <si>
+    <t>Екатеринова</t>
+  </si>
+  <si>
+    <t>Марьяна</t>
+  </si>
+  <si>
+    <t>Марьева</t>
+  </si>
+  <si>
+    <t>Максимовна</t>
+  </si>
+  <si>
+    <t>Роман</t>
+  </si>
+  <si>
+    <t>Романов</t>
+  </si>
+  <si>
+    <t>Романович</t>
+  </si>
+  <si>
+    <t>Александра</t>
+  </si>
+  <si>
+    <t>Александрова</t>
+  </si>
+  <si>
+    <t>Александровна</t>
+  </si>
+  <si>
+    <t>Андрей</t>
+  </si>
+  <si>
+    <t>Андреев</t>
+  </si>
+  <si>
+    <t>Андреевич</t>
+  </si>
+  <si>
+    <t>Вадим</t>
+  </si>
+  <si>
+    <t>Вадимиров</t>
+  </si>
+  <si>
+    <t>Вадимович</t>
+  </si>
+  <si>
+    <t>Светлана</t>
+  </si>
+  <si>
+    <t>Светланова</t>
+  </si>
+  <si>
+    <t>Ивановна</t>
+  </si>
+  <si>
+    <t>Вячеслав</t>
+  </si>
+  <si>
+    <t>Вячеславов</t>
+  </si>
+  <si>
+    <t>Вячеславович</t>
+  </si>
+  <si>
+    <t>Игорь</t>
+  </si>
+  <si>
+    <t>Игорев</t>
+  </si>
+  <si>
+    <t>Игоревич</t>
+  </si>
+  <si>
+    <t>Дмитрий</t>
+  </si>
+  <si>
+    <t>Дмитриев</t>
+  </si>
+  <si>
+    <t>Дмитриевич</t>
+  </si>
+  <si>
+    <t>Николай</t>
+  </si>
+  <si>
+    <t>Николаев</t>
+  </si>
+  <si>
+    <t>Николаевич</t>
+  </si>
+  <si>
+    <t>Яна</t>
+  </si>
+  <si>
+    <t>Янова</t>
+  </si>
+  <si>
+    <t>Николаева</t>
+  </si>
+  <si>
+    <t>Евгений</t>
+  </si>
+  <si>
+    <t>Ивгениев</t>
+  </si>
+  <si>
+    <t>Евгеньевич</t>
+  </si>
+  <si>
+    <t>Сергей</t>
+  </si>
+  <si>
+    <t>Сергеев</t>
   </si>
   <si>
     <t>Сергеевич</t>
   </si>
   <si>
-    <t>10Т 10К</t>
-  </si>
-  <si>
-    <t>Teacher</t>
+    <t>Даниил</t>
+  </si>
+  <si>
+    <t>Данилов</t>
+  </si>
+  <si>
+    <t>Данилович</t>
+  </si>
+  <si>
+    <t>Ксения</t>
+  </si>
+  <si>
+    <t>Ксеньева</t>
+  </si>
+  <si>
+    <t>Вероника</t>
+  </si>
+  <si>
+    <t>Веронова</t>
   </si>
 </sst>
 </file>
@@ -1233,11 +1389,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="10.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="12.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="13.4545454545455" customWidth="1"/>
+    <col min="3" max="3" width="13.7272727272727" customWidth="1"/>
     <col min="4" max="4" width="12.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1283,10 +1440,10 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1294,19 +1451,325 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/exel/users.xlsx
+++ b/exel/users.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>Имя</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Владимирович</t>
-  </si>
-  <si>
-    <t>10T</t>
   </si>
   <si>
     <t>Максим</t>
@@ -1443,7 +1440,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1451,30 +1448,30 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -1485,16 +1482,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1502,16 +1499,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1519,16 +1516,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1536,16 +1533,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1553,16 +1550,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>34</v>
       </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1570,16 +1567,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1587,16 +1584,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1604,16 +1601,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1621,16 +1618,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1638,16 +1635,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1655,16 +1652,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" t="s">
         <v>51</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>52</v>
       </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1672,16 +1669,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s">
         <v>54</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>55</v>
       </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1689,16 +1686,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
         <v>57</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>58</v>
       </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1706,16 +1703,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
         <v>60</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>61</v>
       </c>
-      <c r="C19" t="s">
-        <v>62</v>
-      </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1723,16 +1720,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
         <v>63</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>64</v>
       </c>
-      <c r="C20" t="s">
-        <v>65</v>
-      </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1740,16 +1737,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" t="s">
         <v>66</v>
       </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1757,16 +1754,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" t="s">
         <v>68</v>
       </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
